--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,79 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,50 +738,53 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E8" s="3">
         <v>102700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>98200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>71400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,29 +794,32 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E9" s="3">
         <v>5200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,29 +850,32 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E10" s="3">
         <v>97500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>92600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>66100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,50 +930,51 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E12" s="3">
         <v>30000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1040,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1077,8 +1096,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1152,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,50 +1173,51 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E17" s="3">
         <v>84000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>78000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>73500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>66500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>55000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8900</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1201,50 +1227,53 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>18700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-44600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-54700</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-28300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54400</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-8500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1283,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,49 +1307,50 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3">
         <v>3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-5200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1328,50 +1361,53 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E21" s="3">
         <v>22700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-41900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-53700</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-28300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-59600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-8600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1417,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1407,23 +1446,23 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1434,50 +1473,53 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E23" s="3">
         <v>22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-53900</v>
       </c>
       <c r="I23" s="3">
         <v>-53900</v>
       </c>
       <c r="J23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-47700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-59600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1487,49 +1529,52 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1540,8 +1585,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,50 +1641,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E26" s="3">
         <v>20900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-42700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-53800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-54100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-47800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-59600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,50 +1697,53 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E27" s="3">
         <v>20900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-42700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-53800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-54100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-47800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-59600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,8 +1753,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,49 +1977,52 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>5200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1964,50 +2033,53 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E33" s="3">
         <v>20900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-42700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-53800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-54100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-47800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-59600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2089,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,50 +2145,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E35" s="3">
         <v>20900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-42700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-53800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-54100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-47800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-59600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,55 +2201,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2181,8 +2262,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,41 +2308,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E41" s="3">
         <v>135300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>247800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>114600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>62500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>107700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>110400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>50200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,41 +2362,44 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E42" s="3">
         <v>219800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>109500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>231100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>284400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>54900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>139200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>144800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>45900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>49000</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,29 +2418,32 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E43" s="3">
         <v>29400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>33500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2459,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2382,29 +2474,32 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E44" s="3">
         <v>32400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>24900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2420,8 +2515,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2435,41 +2530,44 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E45" s="3">
         <v>17300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,41 +2586,44 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>464700</v>
+      </c>
+      <c r="E46" s="3">
         <v>434100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>427400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>389100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>382100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>172200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>216100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>265500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>105000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>129900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,8 +2642,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2594,41 +2698,44 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E48" s="3">
         <v>7000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>8100</v>
       </c>
       <c r="H48" s="3">
         <v>8100</v>
       </c>
       <c r="I48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J48" s="3">
         <v>8200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2754,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2810,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,40 +2922,43 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E52" s="3">
         <v>25500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1200</v>
       </c>
       <c r="H52" s="3">
         <v>1200</v>
       </c>
       <c r="I52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="J52" s="3">
         <v>900</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>200</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2859,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,41 +3034,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>517500</v>
+      </c>
+      <c r="E54" s="3">
         <v>466600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>453600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>408000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>391500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>181400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>225200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>274400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>105600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>130500</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,41 +3136,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3060,8 +3190,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3090,11 +3223,11 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3113,41 +3246,44 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E59" s="3">
         <v>39200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>40800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11900</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,41 +3302,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E60" s="3">
         <v>45600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>64100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>46600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3358,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3272,40 +3414,43 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5800</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3325,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,41 +3638,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E66" s="3">
         <v>48200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>67200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3691,13 +3858,13 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>239400</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -3717,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,41 +3940,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-304900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-309700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-330600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-352600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-354200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-311500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-257800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-203700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-155800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-127500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,41 +4164,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>433400</v>
+      </c>
+      <c r="E76" s="3">
         <v>418400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>386400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>352600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>340600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>144000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>192800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>240900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-151200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-124100</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,55 +4276,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4146,50 +4337,53 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E81" s="3">
         <v>20900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-42700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-53800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-54100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-47800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-59600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,8 +4393,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4417,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4232,7 +4430,7 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -4241,11 +4439,11 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -4261,8 +4459,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4273,8 +4471,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,50 +4751,53 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-49700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-43100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-46500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-40600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-46600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,8 +4831,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4621,37 +4841,37 @@
         <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="F91" s="3">
         <v>-300</v>
       </c>
       <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4665,8 +4885,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,50 +4997,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-108100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>123200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>56000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-228200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>84000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-99300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-49200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +5053,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,50 +5299,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>232200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>159600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>25900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,34 +5355,37 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5148,8 +5396,8 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -5163,50 +5411,53 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-112500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>133200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>52000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-45200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>60400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>63800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5214,6 +5465,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,53 +742,56 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E8" s="3">
         <v>108400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>102700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>98200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>400</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -797,32 +801,35 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E9" s="3">
         <v>9400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -853,32 +860,35 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E10" s="3">
         <v>99000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>92600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>66100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,53 +944,54 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E12" s="3">
         <v>44900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>29000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>30600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,31 +1060,34 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>92500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,53 +1200,54 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>210800</v>
+      </c>
+      <c r="E17" s="3">
         <v>106500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>84000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>78000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>73500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>66500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8900</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,53 +1257,56 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-122200</v>
+      </c>
+      <c r="E18" s="3">
         <v>1900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-44600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-54700</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>-28300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-54400</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,52 +1341,53 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-5200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1364,53 +1398,56 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-118200</v>
+      </c>
+      <c r="E21" s="3">
         <v>6800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>24300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-41900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-53700</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-28300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-59600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,52 +1457,55 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1476,53 +1516,56 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-118600</v>
+      </c>
+      <c r="E23" s="3">
         <v>6500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>24000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-53900</v>
       </c>
       <c r="J23" s="3">
         <v>-53900</v>
       </c>
       <c r="K23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="L23" s="3">
         <v>-47700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-59600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1532,52 +1575,55 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,53 +1693,56 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E26" s="3">
         <v>4700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-42700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-53800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-54100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-47800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-59600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,53 +1752,56 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E27" s="3">
         <v>4700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-42700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-53800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-54100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-47800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-59600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,52 +2047,55 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>5200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2036,53 +2106,56 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E33" s="3">
         <v>4700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-42700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-53800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-54100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-47800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-59600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,53 +2224,56 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E35" s="3">
         <v>4700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-42700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-53800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-54100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-47800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-59600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,58 +2283,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2347,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,44 +2395,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>170600</v>
+      </c>
+      <c r="E41" s="3">
         <v>170200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>135300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>247800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>114600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>62500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>107700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>67400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>110400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,44 +2452,47 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>202700</v>
+      </c>
+      <c r="E42" s="3">
         <v>201200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>219800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>109500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>231100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>284400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>54900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>139200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>144800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>45900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>49000</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2421,32 +2511,35 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E43" s="3">
         <v>40100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>33500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2462,8 +2555,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2477,32 +2570,35 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
         <v>38300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2518,8 +2614,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2533,44 +2629,47 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E45" s="3">
         <v>14900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,44 +2688,47 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>410500</v>
+      </c>
+      <c r="E46" s="3">
         <v>464700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>434100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>427400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>389100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>382100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>172200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>216100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>265500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>105000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>129900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2701,44 +2806,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E48" s="3">
         <v>6400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>8100</v>
       </c>
       <c r="I48" s="3">
         <v>8100</v>
       </c>
       <c r="J48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K48" s="3">
         <v>8200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,8 +2865,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,43 +3042,46 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>46400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1200</v>
       </c>
       <c r="I52" s="3">
         <v>1200</v>
       </c>
       <c r="J52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
       </c>
       <c r="L52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>200</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,44 +3160,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>417500</v>
+      </c>
+      <c r="E54" s="3">
         <v>517500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>466600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>453600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>408000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>391500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>181400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>225200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>274400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>105600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>130500</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,44 +3267,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E57" s="3">
         <v>22100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3226,11 +3360,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3249,44 +3383,47 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E59" s="3">
         <v>60000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>39400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,44 +3442,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E60" s="3">
         <v>82000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>45600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>64100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,8 +3501,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3417,43 +3560,46 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5800</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,44 +3796,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E66" s="3">
         <v>84000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>67200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3861,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>239400</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,44 +4114,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-423700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-304900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-309700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-330600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-352600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-354200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-311500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-257800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-203700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-155800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-127500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,44 +4350,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>324400</v>
+      </c>
+      <c r="E76" s="3">
         <v>433400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>418400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>386400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>352600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>340600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>144000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>192800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>240900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-151200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-124100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,58 +4468,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,53 +4532,56 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="E81" s="3">
         <v>4700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-42700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-53800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-54100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-47800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-59600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4433,7 +4632,7 @@
         <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -4442,11 +4641,11 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -4462,8 +4661,8 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,53 +4968,56 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>13600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-49700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-43100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-46500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-40600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-46600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,49 +5052,50 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-400</v>
       </c>
       <c r="F91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
       </c>
       <c r="H91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-200</v>
       </c>
       <c r="M91" s="3">
         <v>-200</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,53 +5227,56 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>800</v>
+      </c>
+      <c r="E94" s="3">
         <v>20900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-108100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>123200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>56000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-228200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>84000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-99300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-49200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,53 +5545,56 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>232200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>159600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>25900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,37 +5604,40 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5399,8 +5648,8 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -5414,53 +5663,56 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>34900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-112500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>133200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>52000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-45200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-43000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>60400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>63800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,86 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -745,56 +746,59 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>88600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>108400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>102700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>98200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>400</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -804,35 +808,38 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E9" s="3">
         <v>23900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -863,35 +870,38 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>64700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>99000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>97500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>92600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>66100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,56 +958,57 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E12" s="3">
         <v>36600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>44900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>30600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,17 +1080,20 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E14" s="3">
         <v>92500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1089,8 +1109,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,56 +1227,57 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E17" s="3">
         <v>210800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>106500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>84000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>78000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>73500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>66500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8900</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,56 +1287,59 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-122200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-54700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-28300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-54400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-8500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1349,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,55 +1375,56 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1401,56 +1435,59 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-118200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>22700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>24300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-41900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-53700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-28300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-59600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-8600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1497,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1486,29 +1526,29 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1519,56 +1559,59 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-118600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-53900</v>
       </c>
       <c r="K23" s="3">
         <v>-53900</v>
       </c>
       <c r="L23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="M23" s="3">
         <v>-47700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-59600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8600</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,55 +1621,58 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,56 +1745,59 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-118800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-42700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-53800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-54100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-47800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-59600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8600</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,56 +1807,59 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-118800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-42700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-53800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-54100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-47800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-59600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1814,8 +1869,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,55 +2117,58 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2109,56 +2179,59 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-118800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-42700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-53800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-54100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-47800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-59600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,8 +2241,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,56 +2303,59 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-118800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-42700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-53800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-54100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-47800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-59600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,61 +2365,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2350,8 +2432,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,47 +2482,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E41" s="3">
         <v>170600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>170200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>135300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>247800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>114600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>62500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>107700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>67400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>110400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>50200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,47 +2542,50 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>234800</v>
+      </c>
+      <c r="E42" s="3">
         <v>202700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>201200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>219800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>109500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>231100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>284400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>54900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>139200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>144800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>45900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>49000</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2514,35 +2604,38 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E43" s="3">
         <v>20400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>40100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>29400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>33500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2558,8 +2651,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2573,8 +2666,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2582,26 +2678,26 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
         <v>38300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,8 +2713,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2632,47 +2728,50 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E45" s="3">
         <v>16900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>17300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,47 +2790,50 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>326700</v>
+      </c>
+      <c r="E46" s="3">
         <v>410500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>464700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>434100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>427400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>389100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>382100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>172200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>216100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>265500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>105000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>129900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +2852,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2809,47 +2914,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>8100</v>
       </c>
       <c r="J48" s="3">
         <v>8100</v>
       </c>
       <c r="K48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="L48" s="3">
         <v>8200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2868,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,8 +3162,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3054,37 +3174,37 @@
         <v>1200</v>
       </c>
       <c r="E52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F52" s="3">
         <v>46400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1200</v>
       </c>
       <c r="J52" s="3">
         <v>1200</v>
       </c>
       <c r="K52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>200</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,47 +3286,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>332200</v>
+      </c>
+      <c r="E54" s="3">
         <v>417500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>517500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>466600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>453600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>408000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>391500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>181400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>225200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>274400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>105600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>130500</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,47 +3398,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="3">
         <v>21500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,8 +3458,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3363,11 +3497,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3386,47 +3520,50 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E59" s="3">
         <v>70200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>60000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>39200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>39400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>40400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,47 +3582,50 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E60" s="3">
         <v>91600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>45600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>64100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>51600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,8 +3644,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3563,46 +3706,49 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5800</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,47 +3954,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E66" s="3">
         <v>93000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>84000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>67200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>55300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4032,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>239400</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,47 +4288,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-496400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-423700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-304900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-309700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-330600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-352600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-354200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-311500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-257800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-203700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-155800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-127500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,47 +4536,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>261300</v>
+      </c>
+      <c r="E76" s="3">
         <v>324400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>433400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>418400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>386400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>352600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>340600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>144000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>192800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>240900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-151200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-124100</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,61 +4660,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4535,56 +4727,59 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-118800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-42700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-53800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-54100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-47800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-59600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4594,8 +4789,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,13 +4815,14 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
@@ -4635,7 +4834,7 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -4644,11 +4843,11 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
+        <v>200</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -4664,8 +4863,8 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,56 +5185,59 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-49700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-43100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-46500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-40600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-46600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,8 +5273,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5062,43 +5283,43 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-400</v>
       </c>
       <c r="G91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="H91" s="3">
         <v>-300</v>
       </c>
       <c r="I91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,56 +5457,59 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E94" s="3">
         <v>800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>20900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-108100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>123200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>56000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-228200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>84000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-99300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5289,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,56 +5791,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>232200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>159600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>25900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5607,40 +5853,43 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5651,8 +5900,8 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -5666,56 +5915,59 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-95600</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>34900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-112500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>133200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>52000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-45200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-43000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>60400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>63800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7900</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5723,6 +5975,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,90 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,59 +750,62 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>88600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>108400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>102700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>98200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,38 +815,41 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>7400</v>
+        <v>58200</v>
       </c>
       <c r="E9" s="3">
-        <v>23900</v>
+        <v>30800</v>
       </c>
       <c r="F9" s="3">
-        <v>9400</v>
+        <v>153000</v>
       </c>
       <c r="G9" s="3">
-        <v>5200</v>
+        <v>54300</v>
       </c>
       <c r="H9" s="3">
-        <v>5600</v>
+        <v>35300</v>
       </c>
       <c r="I9" s="3">
-        <v>5300</v>
+        <v>34600</v>
       </c>
       <c r="J9" s="3">
+        <v>29500</v>
+      </c>
+      <c r="K9" s="3">
         <v>2800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,38 +880,41 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-57800</v>
       </c>
       <c r="E10" s="3">
-        <v>64700</v>
+        <v>-31800</v>
       </c>
       <c r="F10" s="3">
-        <v>99000</v>
+        <v>-64400</v>
       </c>
       <c r="G10" s="3">
-        <v>97500</v>
+        <v>54200</v>
       </c>
       <c r="H10" s="3">
-        <v>92600</v>
+        <v>67400</v>
       </c>
       <c r="I10" s="3">
-        <v>66100</v>
+        <v>63600</v>
       </c>
       <c r="J10" s="3">
+        <v>42000</v>
+      </c>
+      <c r="K10" s="3">
         <v>19100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,59 +972,60 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E12" s="3">
         <v>23300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>44900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>21500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>30600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,22 +1100,25 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>22900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>92500</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>-9900</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1112,8 +1132,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1145,31 +1165,34 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,59 +1254,60 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E17" s="3">
         <v>75300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>210800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>106500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>84000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>78000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>73500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>66500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8900</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,59 +1317,62 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-75700</v>
       </c>
       <c r="E18" s="3">
-        <v>-122200</v>
+        <v>-76300</v>
       </c>
       <c r="F18" s="3">
+        <v>-122100</v>
+      </c>
+      <c r="G18" s="3">
         <v>1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-44600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-54700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-28300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-54400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-8500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,58 +1409,59 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>3600</v>
+        <v>500</v>
       </c>
       <c r="F20" s="3">
-        <v>4600</v>
+        <v>700</v>
       </c>
       <c r="G20" s="3">
-        <v>3700</v>
+        <v>9800</v>
       </c>
       <c r="H20" s="3">
-        <v>3800</v>
+        <v>500</v>
       </c>
       <c r="I20" s="3">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-5200</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1438,59 +1472,62 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-75600</v>
       </c>
       <c r="E21" s="3">
-        <v>-118200</v>
+        <v>-76600</v>
       </c>
       <c r="F21" s="3">
-        <v>6800</v>
+        <v>-122600</v>
       </c>
       <c r="G21" s="3">
-        <v>22700</v>
+        <v>-7500</v>
       </c>
       <c r="H21" s="3">
-        <v>24300</v>
+        <v>18500</v>
       </c>
       <c r="I21" s="3">
-        <v>1600</v>
+        <v>20400</v>
       </c>
       <c r="J21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-41900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-53700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-28300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-59600</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-8600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,58 +1537,61 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1562,8 +1602,11 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1571,50 +1614,50 @@
         <v>-72700</v>
       </c>
       <c r="E23" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-118600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-53900</v>
       </c>
       <c r="L23" s="3">
         <v>-53900</v>
       </c>
       <c r="M23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="N23" s="3">
         <v>-47700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-59600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8600</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,58 +1667,61 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,8 +1797,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1757,50 +1809,50 @@
         <v>-72700</v>
       </c>
       <c r="E26" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-118800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-53800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-54100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-47800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-59600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8600</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,8 +1862,11 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1819,50 +1874,50 @@
         <v>-72700</v>
       </c>
       <c r="E27" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-118800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-53800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-54100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-47800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-59600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8600</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +1927,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,58 +2187,61 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-3600</v>
+        <v>-500</v>
       </c>
       <c r="F32" s="3">
-        <v>-4600</v>
+        <v>-700</v>
       </c>
       <c r="G32" s="3">
-        <v>-3700</v>
+        <v>-9800</v>
       </c>
       <c r="H32" s="3">
-        <v>-3800</v>
+        <v>-500</v>
       </c>
       <c r="I32" s="3">
-        <v>-3500</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>5200</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2182,8 +2252,11 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2191,50 +2264,50 @@
         <v>-72700</v>
       </c>
       <c r="E33" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-118800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-42700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-53800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-54100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-47800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-59600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8600</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2317,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,8 +2382,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2315,50 +2394,50 @@
         <v>-72700</v>
       </c>
       <c r="E35" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-118800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-42700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-53800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-54100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-47800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-59600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8600</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,64 +2447,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2517,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E41" s="3">
         <v>75000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>170600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>170200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>135300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>247800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>114600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>62500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>107700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>67400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>110400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>50200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,50 +2632,53 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>162600</v>
+      </c>
+      <c r="E42" s="3">
         <v>234800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>202700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>201200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>219800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>109500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>231100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>284400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>139200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>144800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>49000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,38 +2697,41 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4100</v>
+        <v>1700</v>
       </c>
       <c r="E43" s="3">
-        <v>20400</v>
+        <v>4200</v>
       </c>
       <c r="F43" s="3">
-        <v>40100</v>
+        <v>20700</v>
       </c>
       <c r="G43" s="3">
-        <v>29400</v>
+        <v>40600</v>
       </c>
       <c r="H43" s="3">
-        <v>33500</v>
+        <v>29500</v>
       </c>
       <c r="I43" s="3">
+        <v>34300</v>
+      </c>
+      <c r="J43" s="3">
         <v>17600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2654,8 +2747,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2669,38 +2762,41 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
         <v>38300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2716,8 +2812,8 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2731,50 +2827,53 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>12800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>16900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>14900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>17300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>11800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>12700</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>10100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,50 +2892,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>245300</v>
+      </c>
+      <c r="E46" s="3">
         <v>326700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>410500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>464700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>434100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>427400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>389100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>382100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>172200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>216100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>265500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>105000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>129900</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,31 +2957,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2917,50 +3022,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>8100</v>
       </c>
       <c r="K48" s="3">
         <v>8100</v>
       </c>
       <c r="L48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="M48" s="3">
         <v>8200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,8 +3087,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,49 +3282,52 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1200</v>
+        <v>1900</v>
       </c>
       <c r="E52" s="3">
         <v>1200</v>
       </c>
       <c r="F52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G52" s="3">
         <v>46400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1200</v>
       </c>
       <c r="K52" s="3">
         <v>1200</v>
       </c>
       <c r="L52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="M52" s="3">
         <v>900</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>200</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>250700</v>
+      </c>
+      <c r="E54" s="3">
         <v>332200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>417500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>517500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>466600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>453600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>408000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>391500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>181400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>225200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>274400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>105600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>130500</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,50 +3529,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>5000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,31 +3592,34 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3500,11 +3634,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>65100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>70200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>60000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>39200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>39400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>40800</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>40400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E60" s="3">
         <v>70100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>91600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>64100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>46600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,31 +3787,34 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3709,49 +3852,52 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>4200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5800</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E66" s="3">
         <v>70900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>93000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>84000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>67200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>50800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4203,13 +4371,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>239400</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-569100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-496400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-423700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-304900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-309700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-330600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-352600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-354200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-311500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-257800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-203700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-155800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-127500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E76" s="3">
         <v>261300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>324400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>433400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>418400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>386400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>352600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>340600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>144000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>192800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>240900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-151200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-124100</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,64 +4852,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,8 +4922,11 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4739,50 +4934,50 @@
         <v>-72700</v>
       </c>
       <c r="E81" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-118800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-42700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-53800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-54100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-47800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-59600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8600</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4987,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,41 +5014,42 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
       </c>
       <c r="L83" s="3">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -4866,8 +5065,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,59 +5402,62 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-66600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-49700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-43100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-46500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-40600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-46600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,55 +5494,56 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-36200</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-400</v>
       </c>
       <c r="H91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="I91" s="3">
         <v>-300</v>
       </c>
       <c r="J91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
       </c>
       <c r="O91" s="3">
         <v>-200</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,59 +5687,62 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>20900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-108100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>123200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>56000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-228200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>84000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-99300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-49200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,31 +5779,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,59 +6037,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>232200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>159600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>25900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,43 +6102,46 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>500</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>200</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>-100</v>
       </c>
       <c r="N101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -5903,8 +6152,8 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -5918,59 +6167,62 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-95600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-112500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>133200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>52000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-45200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-43000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>60400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7900</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,94 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,62 +753,65 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>88600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>108400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>102700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>98200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>71400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3">
         <v>400</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -818,41 +821,44 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E9" s="3">
         <v>58200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>153000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>34600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>29500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -883,41 +889,44 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-57800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-31800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-64400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>54200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>67400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>63600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>42000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -948,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,62 +985,63 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E12" s="3">
         <v>57400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>36600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>44900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>30600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,13 +1119,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-9900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1117,12 +1136,12 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-9900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1135,8 +1154,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1168,8 +1187,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1180,7 +1202,7 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
@@ -1192,11 +1214,11 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1233,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,62 +1280,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E17" s="3">
         <v>76100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>75300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>210800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>106500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>84000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>78000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>73500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>66500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>47800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8900</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,62 +1346,65 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-75700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-76300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-122100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-44600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-28300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-54400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-8500</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,61 +1442,62 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1475,62 +1508,65 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-50200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-75600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-76600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-122600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>20400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-41900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-53700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-28300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-8600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1576,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1566,35 +1605,35 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1605,62 +1644,65 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-72700</v>
+        <v>-38200</v>
       </c>
       <c r="E23" s="3">
         <v>-72700</v>
       </c>
       <c r="F23" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="G23" s="3">
         <v>-118600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-53900</v>
       </c>
       <c r="M23" s="3">
         <v>-53900</v>
       </c>
       <c r="N23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="O23" s="3">
         <v>-47700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8600</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1670,61 +1712,64 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-600</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1735,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,62 +1848,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-72700</v>
+        <v>-37500</v>
       </c>
       <c r="E26" s="3">
         <v>-72700</v>
       </c>
       <c r="F26" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-118800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>20900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-42700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-53800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-47800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8600</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,62 +1916,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-72700</v>
+        <v>-37500</v>
       </c>
       <c r="E27" s="3">
         <v>-72700</v>
       </c>
       <c r="F27" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-118800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>20900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-42700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-53800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-47800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,61 +2256,64 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>5200</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2255,62 +2324,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-72700</v>
+        <v>-37500</v>
       </c>
       <c r="E33" s="3">
         <v>-72700</v>
       </c>
       <c r="F33" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="G33" s="3">
         <v>-118800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>20900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-42700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-53800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-47800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,62 +2460,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-72700</v>
+        <v>-37500</v>
       </c>
       <c r="E35" s="3">
         <v>-72700</v>
       </c>
       <c r="F35" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="G35" s="3">
         <v>-118800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>20900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-42700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-53800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-47800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2520,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,53 +2655,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E41" s="3">
         <v>71800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>75000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>170600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>170200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>135300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>247800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>114600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>62500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>107700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>67400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>110400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,53 +2721,56 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E42" s="3">
         <v>162600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>234800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>202700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>201200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>219800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>109500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>231100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>284400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>54900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>139200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>144800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>49000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,41 +2789,44 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>34300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +2842,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2765,8 +2857,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2779,27 +2874,27 @@
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>38300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +2910,8 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -2830,8 +2925,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2856,27 +2954,27 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>10100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,53 +2993,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>189400</v>
+      </c>
+      <c r="E46" s="3">
         <v>245300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>326700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>410500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>464700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>434100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>427400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>389100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>382100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>172200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>216100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>265500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>105000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>129900</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2986,8 +3090,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3025,53 +3129,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>8100</v>
       </c>
       <c r="L48" s="3">
         <v>8100</v>
       </c>
       <c r="M48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="N48" s="3">
         <v>8200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,8 +3197,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,52 +3401,55 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1200</v>
       </c>
       <c r="F52" s="3">
         <v>1200</v>
       </c>
       <c r="G52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H52" s="3">
         <v>46400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1200</v>
       </c>
       <c r="L52" s="3">
         <v>1200</v>
       </c>
       <c r="M52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="N52" s="3">
         <v>900</v>
       </c>
       <c r="O52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>200</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3350,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,53 +3537,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>193600</v>
+      </c>
+      <c r="E54" s="3">
         <v>250700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>332200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>417500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>517500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>466600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>453600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>408000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>391500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>181400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>225200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>274400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>105600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>130500</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,53 +3659,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,34 +3725,37 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2300</v>
       </c>
       <c r="G58" s="3">
         <v>2300</v>
       </c>
       <c r="H58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I58" s="3">
         <v>2200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2100</v>
       </c>
       <c r="J58" s="3">
         <v>2100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3637,11 +3770,11 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,8 +3793,11 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3686,27 +3822,27 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>40400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,53 +3861,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E60" s="3">
         <v>53900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>91600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>64100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,35 +3929,38 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3855,8 +3997,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3881,26 +4026,26 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>4200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5800</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3920,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,53 +4269,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E66" s="3">
         <v>54500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>70900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>93000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>84000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>67200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4374,13 +4541,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>239400</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -4400,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,53 +4635,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-606700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-569100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-496400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-423700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-304900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-309700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-330600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-352600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-354200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-311500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-257800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-203700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-155800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-127500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,53 +4907,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E76" s="3">
         <v>196200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>261300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>324400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>433400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>418400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>386400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>352600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>340600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>144000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>192800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>240900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-151200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-124100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4925,62 +5116,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-72700</v>
+        <v>-37500</v>
       </c>
       <c r="E81" s="3">
         <v>-72700</v>
       </c>
       <c r="F81" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="G81" s="3">
         <v>-118800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>20900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-42700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-53800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-47800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4990,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5212,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5027,7 +5225,7 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -5036,23 +5234,23 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -5068,8 +5266,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5080,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,62 +5618,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-41600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-66600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-49700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-43100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-46500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-40600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,58 +5714,59 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-400</v>
       </c>
       <c r="I91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J91" s="3">
         <v>-300</v>
       </c>
       <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-200</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5560,8 +5780,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,62 +5916,65 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E94" s="3">
         <v>38800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>20900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-108100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>123200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>56000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-228200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>84000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-99300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5755,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5806,8 +6039,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5845,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,8 +6282,11 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6049,53 +6294,53 @@
         <v>100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>232200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>159600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>25900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,46 +6350,49 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-100</v>
       </c>
       <c r="N101" s="3">
         <v>-100</v>
       </c>
       <c r="O101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6155,8 +6403,8 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -6170,62 +6418,65 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-95600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-112500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>133200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>52000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-45200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-43000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>60400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-26500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>63800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7900</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,65 +757,68 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>88600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>108400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>102700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>98200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>71400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3">
         <v>400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -824,44 +828,47 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E9" s="3">
         <v>-13300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>58200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>153000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>35300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>34600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,44 +899,47 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E10" s="3">
         <v>12600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-57800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-31800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-64400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>63600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>42000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,65 +999,66 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E12" s="3">
         <v>36200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>57400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>36600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>44900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>21500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>30600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,29 +1139,32 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-9900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-9900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1157,8 +1177,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1190,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,7 +1228,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1217,11 +1240,11 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
+        <v>300</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,65 +1307,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E17" s="3">
         <v>40000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>76100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>75300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>210800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>106500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>84000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>78000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>73500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>66500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8900</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,65 +1376,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-40700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-75700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-76300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-122100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-44600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-54700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-54400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-8500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,8 +1447,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,64 +1476,65 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>9700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-5200</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1511,65 +1545,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-50200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-75600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-76600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-122600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>20400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-41900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-53700</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-59600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-8600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1608,35 +1648,35 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1647,65 +1687,68 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-38200</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-72700</v>
       </c>
       <c r="F23" s="3">
         <v>-72700</v>
       </c>
       <c r="G23" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="H23" s="3">
         <v>-118600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-53900</v>
       </c>
       <c r="N23" s="3">
         <v>-53900</v>
       </c>
       <c r="O23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="P23" s="3">
         <v>-47700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-59600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1715,64 +1758,67 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-600</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,65 +1900,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-72700</v>
       </c>
       <c r="F26" s="3">
         <v>-72700</v>
       </c>
       <c r="G26" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="H26" s="3">
         <v>-118800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-53800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-54100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-47800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-59600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8600</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1919,65 +1971,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-37500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-72700</v>
       </c>
       <c r="F27" s="3">
         <v>-72700</v>
       </c>
       <c r="G27" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="H27" s="3">
         <v>-118800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-42700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-53800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-54100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-47800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-59600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8600</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1987,8 +2042,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,64 +2326,67 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>5200</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2327,65 +2397,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37500</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-72700</v>
       </c>
       <c r="F33" s="3">
         <v>-72700</v>
       </c>
       <c r="G33" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="H33" s="3">
         <v>-118800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-42700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-53800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-54100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-47800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-59600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8600</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2395,8 +2468,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,65 +2539,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37500</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-72700</v>
       </c>
       <c r="F35" s="3">
         <v>-72700</v>
       </c>
       <c r="G35" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="H35" s="3">
         <v>-118800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-42700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-53800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-54100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-47800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-59600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8600</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,70 +2610,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2686,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,56 +2742,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E41" s="3">
         <v>77400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>71800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>75000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>170600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>170200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>135300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>247800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>114600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>62500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>107700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>67400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>110400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,56 +2811,59 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>144300</v>
+      </c>
+      <c r="E42" s="3">
         <v>99100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>162600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>234800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>202700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>201200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>219800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>109500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>231100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>284400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>54900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>139200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>144800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>45900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>49000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,44 +2882,47 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>34300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2845,8 +2938,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2860,8 +2953,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2877,27 +2973,27 @@
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>38300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>32400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>24900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2913,8 +3009,8 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -2928,8 +3024,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2957,27 +3056,27 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>10100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,56 +3095,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E46" s="3">
         <v>189400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>245300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>326700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>410500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>464700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>434100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>427400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>389100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>382100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>172200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>216100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>265500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>105000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>129900</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3166,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3093,8 +3198,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3132,56 +3237,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>8100</v>
       </c>
       <c r="M48" s="3">
         <v>8100</v>
       </c>
       <c r="N48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="O48" s="3">
         <v>8200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>300</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,8 +3308,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,8 +3521,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3413,46 +3533,46 @@
         <v>1500</v>
       </c>
       <c r="E52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F52" s="3">
         <v>1900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1200</v>
       </c>
       <c r="G52" s="3">
         <v>1200</v>
       </c>
       <c r="H52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I52" s="3">
         <v>46400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1200</v>
       </c>
       <c r="M52" s="3">
         <v>1200</v>
       </c>
       <c r="N52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="O52" s="3">
         <v>900</v>
       </c>
       <c r="P52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>200</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,56 +3663,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>219700</v>
+      </c>
+      <c r="E54" s="3">
         <v>193600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>250700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>332200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>417500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>517500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>466600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>453600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>408000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>391500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>181400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>225200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>274400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>105600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>130500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,56 +3790,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,37 +3859,40 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2300</v>
       </c>
       <c r="H58" s="3">
         <v>2300</v>
       </c>
       <c r="I58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J58" s="3">
         <v>2200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2100</v>
       </c>
       <c r="K58" s="3">
         <v>2100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3773,11 +3907,11 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3796,8 +3930,11 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3825,27 +3962,27 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>40400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,56 +4001,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E60" s="3">
         <v>28400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>82000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>64100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,38 +4072,41 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4000,8 +4143,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4029,26 +4175,26 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>4200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5800</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,56 +4427,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E66" s="3">
         <v>28900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>70900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>93000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>84000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>67200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>50800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4544,13 +4712,13 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>239400</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,56 +4809,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-642600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-606700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-569100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-496400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-423700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-304900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-309700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-330600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-352600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-354200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-311500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-257800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-203700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-155800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-127500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,56 +5093,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E76" s="3">
         <v>164800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>196200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>261300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>324400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>433400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>418400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>386400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>352600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>340600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>144000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>192800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>240900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-151200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-124100</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5235,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,65 +5311,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37500</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-72700</v>
       </c>
       <c r="F81" s="3">
         <v>-72700</v>
       </c>
       <c r="G81" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="H81" s="3">
         <v>-118800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-42700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-53800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-54100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-47800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-59600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8600</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5187,8 +5382,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5228,7 +5427,7 @@
         <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -5237,23 +5436,23 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
       </c>
       <c r="N83" s="3">
+        <v>200</v>
+      </c>
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -5269,8 +5468,8 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,65 +5835,68 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-59000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-66600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-49700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-43100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-46500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-40600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-46600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,8 +5935,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5724,52 +5945,52 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-400</v>
       </c>
       <c r="J91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-200</v>
       </c>
       <c r="Q91" s="3">
         <v>-200</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,65 +6146,68 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E94" s="3">
         <v>65000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>38800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>20900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-108100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>123200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>56000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-228200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>84000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-99300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6042,8 +6276,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,65 +6528,68 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100</v>
+        <v>65700</v>
       </c>
       <c r="E100" s="3">
         <v>100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>232200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>159600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>25900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,49 +6599,52 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6406,8 +6655,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -6421,65 +6670,68 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E102" s="3">
         <v>5600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-95600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-112500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>133200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>52000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-45200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>40600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-43000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>60400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>63800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7900</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,8 +761,11 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -771,57 +775,57 @@
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>88600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>108400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>102700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>98200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
         <v>400</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,47 +835,50 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E9" s="3">
         <v>22100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>-13300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>58200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>153000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>54300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>35300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,47 +909,50 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E10" s="3">
         <v>-22100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-57800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-31800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-64400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>54200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>63600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>42000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,68 +1013,69 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E12" s="3">
         <v>22100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>57400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>36600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>44900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>30600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5000</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,32 +1159,35 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-9900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>22900</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-9900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,8 +1200,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1213,13 +1233,16 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1231,7 +1254,7 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1243,11 +1266,11 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
+        <v>300</v>
+      </c>
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,68 +1334,69 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E17" s="3">
         <v>37800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>76100</v>
       </c>
-      <c r="G17" s="3">
-        <v>75300</v>
-      </c>
       <c r="H17" s="3">
+        <v>52400</v>
+      </c>
+      <c r="I17" s="3">
         <v>210800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>106500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>84000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>78000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>73500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>66500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>54700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8900</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,68 +1406,71 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-40700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-75700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-76300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-122100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-44600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-54700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-28300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-54400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-8500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1480,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,67 +1510,68 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-5200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1548,68 +1582,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-38000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-50200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-75600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-76600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-122600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-41900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-53700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-28300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-59600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-8600</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1656,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1651,35 +1691,35 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1690,68 +1730,71 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-38200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-72700</v>
       </c>
       <c r="G23" s="3">
         <v>-72700</v>
       </c>
       <c r="H23" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-118600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-53900</v>
       </c>
       <c r="O23" s="3">
         <v>-53900</v>
       </c>
       <c r="P23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-47700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-59600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-21900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-14500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8600</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1761,67 +1804,70 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,68 +1952,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-37500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-72700</v>
       </c>
       <c r="G26" s="3">
         <v>-72700</v>
       </c>
       <c r="H26" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-118800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>22100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-42700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-53800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-54100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-59600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8600</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,68 +2026,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-37500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-72700</v>
       </c>
       <c r="G27" s="3">
         <v>-72700</v>
       </c>
       <c r="H27" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-118800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-42700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-53800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-28300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-59600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-21900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8600</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,8 +2100,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,67 +2396,70 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>5200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2400,68 +2470,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-37500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-72700</v>
       </c>
       <c r="G33" s="3">
         <v>-72700</v>
       </c>
       <c r="H33" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-118800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-42700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-53800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-28300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-59600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8600</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2544,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,68 +2618,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-37500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-72700</v>
       </c>
       <c r="G35" s="3">
         <v>-72700</v>
       </c>
       <c r="H35" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-118800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-42700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-53800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-28300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-59600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8600</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,73 +2692,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2771,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,59 +2829,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E41" s="3">
         <v>59800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>75000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>170600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>170200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>135300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>247800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>114600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>62500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>107700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>67400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>110400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>50200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,59 +2901,62 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E42" s="3">
         <v>144300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>99100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>162600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>234800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>202700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>201200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>219800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>109500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>231100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>284400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>54900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>139200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>144800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>45900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>49000</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,47 +2975,50 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>34300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2941,8 +3034,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2976,27 +3072,27 @@
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>38300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>32400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>600</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3012,8 +3108,8 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3027,8 +3123,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3059,27 +3158,27 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>10100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,59 +3197,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>186900</v>
+      </c>
+      <c r="E46" s="3">
         <v>216100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>189400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>245300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>326700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>410500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>464700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>434100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>427400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>389100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>382100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>172200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>216100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>265500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>105000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>129900</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3201,8 +3306,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3240,59 +3345,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>8100</v>
       </c>
       <c r="N48" s="3">
         <v>8100</v>
       </c>
       <c r="O48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="P48" s="3">
         <v>8200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,8 +3419,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,8 +3641,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3536,46 +3656,46 @@
         <v>1500</v>
       </c>
       <c r="F52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G52" s="3">
         <v>1900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1200</v>
       </c>
       <c r="H52" s="3">
         <v>1200</v>
       </c>
       <c r="I52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J52" s="3">
         <v>46400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1200</v>
       </c>
       <c r="N52" s="3">
         <v>1200</v>
       </c>
       <c r="O52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="P52" s="3">
         <v>900</v>
       </c>
       <c r="Q52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>200</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,59 +3789,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>194600</v>
+      </c>
+      <c r="E54" s="3">
         <v>219700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>193600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>250700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>332200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>417500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>517500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>466600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>453600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>408000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>391500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>181400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>225200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>274400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>105600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>130500</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,59 +3921,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,40 +3993,43 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2300</v>
       </c>
       <c r="I58" s="3">
         <v>2300</v>
       </c>
       <c r="J58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K58" s="3">
         <v>2200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2100</v>
       </c>
       <c r="L58" s="3">
         <v>2100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3910,11 +4044,11 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,8 +4067,11 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3965,27 +4102,27 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>40400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,59 +4141,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E60" s="3">
         <v>17900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>91600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>82000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>45600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>15100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,41 +4215,44 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4146,8 +4289,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4178,26 +4324,26 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>4200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5800</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,59 +4585,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E66" s="3">
         <v>18300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>54500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>93000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>84000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>50800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>33500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4715,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>239400</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,59 +4983,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-684000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-642600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-606700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-569100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-496400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-423700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-304900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-309700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-330600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-352600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-354200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-311500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-257800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-203700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-155800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-127500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,59 +5279,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E76" s="3">
         <v>201400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>164800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>196200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>261300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>324400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>433400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>418400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>386400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>352600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>340600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>144000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>192800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>240900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-151200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-124100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,73 +5427,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,68 +5506,71 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-37500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-72700</v>
       </c>
       <c r="G81" s="3">
         <v>-72700</v>
       </c>
       <c r="H81" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-118800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-42700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-53800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-28300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-59600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8600</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5385,8 +5580,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,13 +5610,14 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
@@ -5430,7 +5629,7 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -5439,23 +5638,23 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
+        <v>200</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
       </c>
       <c r="O83" s="3">
+        <v>200</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -5471,8 +5670,8 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,68 +6052,71 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-39800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-59000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-41600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-66600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-49700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-43100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-46500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-28200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-46600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-12600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6156,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5948,52 +6169,52 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-400</v>
       </c>
       <c r="K91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-200</v>
       </c>
       <c r="R91" s="3">
         <v>-200</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,68 +6376,71 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-43700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>65000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>38800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>20900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-108100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>123200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>56000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-228200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>84000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-99300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6279,8 +6513,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,68 +6774,71 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>65700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>100</v>
       </c>
       <c r="F100" s="3">
         <v>100</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>232200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>159600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>25900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,52 +6848,55 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6658,8 +6907,8 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -6673,68 +6922,71 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-95600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>34900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-112500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>133200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>52000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-45200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>40600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-43000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>60400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>63800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7900</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,109 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -768,8 +768,11 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -785,57 +788,57 @@
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>88600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>108400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>102700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>98200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3">
         <v>400</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -845,53 +848,56 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E9" s="3">
         <v>19900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>27200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22100</v>
       </c>
-      <c r="G9" s="3">
-        <v>-13300</v>
-      </c>
       <c r="H9" s="3">
-        <v>58200</v>
+        <v>22900</v>
       </c>
       <c r="I9" s="3">
+        <v>22000</v>
+      </c>
+      <c r="J9" s="3">
         <v>30800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>153000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>54300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>34600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,53 +928,56 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E10" s="3">
         <v>-19900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-27200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-22100</v>
       </c>
-      <c r="G10" s="3">
-        <v>12600</v>
-      </c>
       <c r="H10" s="3">
-        <v>-57800</v>
+        <v>-23600</v>
       </c>
       <c r="I10" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="J10" s="3">
         <v>-31800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-64400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>54200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>63600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>42000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,74 +1040,75 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E12" s="3">
         <v>19900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22100</v>
       </c>
-      <c r="G12" s="3">
-        <v>36200</v>
-      </c>
       <c r="H12" s="3">
-        <v>57400</v>
+        <v>22900</v>
       </c>
       <c r="I12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="J12" s="3">
         <v>23300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>36600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>44900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>30600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5000</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1105,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,13 +1198,16 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-5500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1196,24 +1215,24 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-9900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3">
+        <v>36200</v>
+      </c>
+      <c r="J14" s="3">
         <v>22900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-9900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1226,8 +1245,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1259,8 +1278,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1271,7 +1293,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
@@ -1283,7 +1305,7 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
@@ -1295,11 +1317,11 @@
         <v>300</v>
       </c>
       <c r="N15" s="3">
+        <v>300</v>
+      </c>
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1336,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,74 +1387,75 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E17" s="3">
         <v>36000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40000</v>
       </c>
-      <c r="H17" s="3">
-        <v>76100</v>
-      </c>
       <c r="I17" s="3">
+        <v>39900</v>
+      </c>
+      <c r="J17" s="3">
         <v>52400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>210800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>106500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>84000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>78000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>73500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>66500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>47800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>54700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8900</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,74 +1465,77 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-36600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-36000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-42900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-40700</v>
       </c>
-      <c r="H18" s="3">
-        <v>-75700</v>
-      </c>
       <c r="I18" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="J18" s="3">
         <v>-53400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-122100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-44600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-54700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-28300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-54400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-8500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1516,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,73 +1577,74 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-5200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1622,74 +1655,77 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-36100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-43300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-38000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-50200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-75600</v>
-      </c>
       <c r="I21" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-53700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-122600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-41900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-28300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-59600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-8600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,8 +1735,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1737,35 +1776,35 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1776,74 +1815,77 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-41400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-38200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-72700</v>
       </c>
       <c r="I23" s="3">
         <v>-72700</v>
       </c>
       <c r="J23" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-118600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-53900</v>
       </c>
       <c r="Q23" s="3">
         <v>-53900</v>
       </c>
       <c r="R23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="S23" s="3">
         <v>-47700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-59600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-21900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-14500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8600</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1853,13 +1895,16 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1867,59 +1912,59 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1930,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,74 +2055,77 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-41400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-72700</v>
       </c>
       <c r="I26" s="3">
         <v>-72700</v>
       </c>
       <c r="J26" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-118800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>22100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-42700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-54100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-47800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-28300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-59600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-21900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-14500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8600</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2084,74 +2135,77 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-41400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-37500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-72700</v>
       </c>
       <c r="I27" s="3">
         <v>-72700</v>
       </c>
       <c r="J27" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-118800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>20900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-42700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-54100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-47800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-28300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-59600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-21900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-14500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8600</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,73 +2535,76 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>5200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2546,74 +2615,77 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-41400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-72700</v>
       </c>
       <c r="I33" s="3">
         <v>-72700</v>
       </c>
       <c r="J33" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-118800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>20900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-42700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-54100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-47800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-28300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-59600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-21900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-14500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8600</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2623,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,74 +2775,77 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-41400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-72700</v>
       </c>
       <c r="I35" s="3">
         <v>-72700</v>
       </c>
       <c r="J35" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-118800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>20900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-42700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-54100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-47800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-28300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-59600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-21900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-14500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8600</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,79 +2855,82 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,65 +3002,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>226700</v>
+      </c>
+      <c r="E41" s="3">
         <v>225200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>58100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>59800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>75000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>170600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>170200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>135300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>247800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>114600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>62500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>107700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>67400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>110400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>50200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>76700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,65 +3080,68 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E42" s="3">
         <v>118800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>122700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>144300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>99100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>162600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>234800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>202700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>201200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>219800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>109500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>231100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>284400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>54900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>139200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>144800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>45900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>49000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3071,8 +3160,11 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3083,41 +3175,41 @@
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3133,8 +3225,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3148,8 +3240,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3174,27 +3269,27 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>38300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>32400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3210,8 +3305,8 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3225,8 +3320,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3263,27 +3361,27 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>10100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,65 +3400,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>323700</v>
+      </c>
+      <c r="E46" s="3">
         <v>353400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>186900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>216100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>189400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>245300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>326700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>410500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>464700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>434100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>427400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>389100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>382100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>172200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>216100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>265500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>105000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>129900</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3417,8 +3521,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3456,65 +3560,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E48" s="3">
         <v>5900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7600</v>
-      </c>
-      <c r="O48" s="3">
-        <v>8100</v>
       </c>
       <c r="P48" s="3">
         <v>8100</v>
       </c>
       <c r="Q48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="R48" s="3">
         <v>8200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3640,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,8 +3880,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3773,7 +3892,7 @@
         <v>3500</v>
       </c>
       <c r="E52" s="3">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="F52" s="3">
         <v>1500</v>
@@ -3782,46 +3901,46 @@
         <v>1500</v>
       </c>
       <c r="H52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I52" s="3">
         <v>1900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1200</v>
       </c>
       <c r="J52" s="3">
         <v>1200</v>
       </c>
       <c r="K52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L52" s="3">
         <v>46400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11300</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1200</v>
       </c>
       <c r="P52" s="3">
         <v>1200</v>
       </c>
       <c r="Q52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="R52" s="3">
         <v>900</v>
       </c>
       <c r="S52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>200</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3841,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,65 +4040,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>332600</v>
+      </c>
+      <c r="E54" s="3">
         <v>362700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>194600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>219700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>193600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>250700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>332200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>417500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>517500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>466600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>453600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>408000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>391500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>181400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>225200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>274400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>105600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>130500</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,65 +4182,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>5300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,46 +4260,49 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2300</v>
       </c>
       <c r="K58" s="3">
         <v>2300</v>
       </c>
       <c r="L58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M58" s="3">
         <v>2200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2100</v>
       </c>
       <c r="N58" s="3">
         <v>2100</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4184,11 +4317,11 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,8 +4340,11 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4245,27 +4381,27 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>40400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,65 +4420,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E60" s="3">
         <v>25800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>70100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>91600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>82000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>64100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>32600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,47 +4500,50 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E61" s="3">
         <v>5000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4438,8 +4580,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4476,26 +4621,26 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>4200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5800</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -4515,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,65 +4900,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E66" s="3">
         <v>30700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>28900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>70900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>93000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>84000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>48200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>50800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5057,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>239400</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -5083,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,65 +5330,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-751400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-718400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-684000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-642600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-606700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-569100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-496400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-423700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-304900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-309700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-330600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-352600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-354200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-311500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-257800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-203700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-155800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-127500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,65 +5650,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>305300</v>
+      </c>
+      <c r="E76" s="3">
         <v>332000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>167900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>201400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>164800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>196200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>261300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>324400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>433400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>418400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>386400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>352600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>340600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>144000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>192800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>240900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-151200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-124100</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,79 +5810,82 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5704,74 +5895,77 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-41400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-72700</v>
       </c>
       <c r="I81" s="3">
         <v>-72700</v>
       </c>
       <c r="J81" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-118800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>20900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-42700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-54100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-47800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-28300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-59600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-21900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-14500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8600</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5781,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5822,7 +6020,7 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
@@ -5834,7 +6032,7 @@
         <v>300</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -5843,23 +6041,23 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -5875,8 +6073,8 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5887,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,74 +6485,77 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-25200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-59000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-41600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-66600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-49700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-46500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-40600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-28200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-46600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6349,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,13 +6597,14 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -6393,55 +6613,55 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-36200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-400</v>
       </c>
       <c r="M91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-200</v>
       </c>
       <c r="T91" s="3">
         <v>-200</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6455,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,74 +6835,77 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E94" s="3">
         <v>5200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>23000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>65000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>38800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>20900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-108100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>123200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>56000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-228200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>84000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>4500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-99300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-49200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6686,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6753,8 +6986,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6792,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,74 +7265,77 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>191600</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>65700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>100</v>
       </c>
       <c r="H100" s="3">
         <v>100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>232200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>159600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>25900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7100,58 +7345,61 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-100</v>
       </c>
       <c r="N101" s="3">
         <v>-100</v>
       </c>
       <c r="O101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>-100</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -7162,8 +7410,8 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -7177,74 +7425,77 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>166600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-95600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-112500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>133200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>52000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-45200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-43000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>60400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-26500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>63800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7252,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="92">
   <si>
     <t>AMLX</t>
   </si>
@@ -656,112 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -771,8 +772,11 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -791,57 +795,57 @@
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>88600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>108400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>102700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>98200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>71400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3">
         <v>400</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,56 +855,59 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E9" s="3">
         <v>21200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>153000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>54300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>34600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -931,56 +938,59 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-21200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-19900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-27200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-22100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-23600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-21600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-31800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-64400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>54200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>63600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1011,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,77 +1054,78 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E12" s="3">
         <v>21200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>36600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>44900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>30000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>30600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5000</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1135,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,41 +1218,44 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-9900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>36200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-9900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1248,8 +1268,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1281,8 +1301,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1296,7 +1319,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1308,7 +1331,7 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>300</v>
@@ -1320,11 +1343,11 @@
         <v>300</v>
       </c>
       <c r="O15" s="3">
+        <v>300</v>
+      </c>
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,77 +1414,78 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E17" s="3">
         <v>36600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>52400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>210800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>106500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>84000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>78000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>73500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>66500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>54300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>54700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8900</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,77 +1495,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-36600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-36000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-42900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-40700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-39500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-53400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-122100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-54700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-28300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-54400</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1578,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,76 +1611,77 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>5200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1658,77 +1692,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-41700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-36100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-43300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-38000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-50200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-39400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-53700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-122600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-41900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-53700</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-28300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-59600</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,8 +1775,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1779,35 +1819,35 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1818,77 +1858,80 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-33000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-41400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-72700</v>
       </c>
       <c r="J23" s="3">
         <v>-72700</v>
       </c>
       <c r="K23" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="L23" s="3">
         <v>-118600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-42100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-53900</v>
       </c>
       <c r="R23" s="3">
         <v>-53900</v>
       </c>
       <c r="S23" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="T23" s="3">
         <v>-47700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-59600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-21900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-14500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1898,16 +1941,19 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1915,59 +1961,59 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,77 +2107,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-33000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-41400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-37500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-72700</v>
       </c>
       <c r="J26" s="3">
         <v>-72700</v>
       </c>
       <c r="K26" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="L26" s="3">
         <v>-118800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>22100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-54100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-47800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-28300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-59600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2138,77 +2190,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-41400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-37500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-72700</v>
       </c>
       <c r="J27" s="3">
         <v>-72700</v>
       </c>
       <c r="K27" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="L27" s="3">
         <v>-118800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-53800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-54100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-47800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-28300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-59600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,8 +2273,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,76 +2605,79 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2618,77 +2688,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-33000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-41400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-37500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-72700</v>
       </c>
       <c r="J33" s="3">
         <v>-72700</v>
       </c>
       <c r="K33" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="L33" s="3">
         <v>-118800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-53800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-54100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-47800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-28300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-59600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,8 +2771,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,77 +2854,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-33000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-41400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-37500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-72700</v>
       </c>
       <c r="J35" s="3">
         <v>-72700</v>
       </c>
       <c r="K35" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="L35" s="3">
         <v>-118800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-53800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-54100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-47800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-28300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-59600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,82 +2937,85 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2943,8 +3025,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,68 +3089,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>229100</v>
+      </c>
+      <c r="E41" s="3">
         <v>226700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>225200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>58100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>75000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>170600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>170200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>135300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>247800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>114600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>62500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>107700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>67400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>110400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>50200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>76700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,68 +3170,71 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E42" s="3">
         <v>90300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>118800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>122700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>144300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>99100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>162600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>234800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>202700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>201200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>219800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>109500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>231100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>284400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>54900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>139200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>144800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>45900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>49000</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,13 +3253,16 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
@@ -3178,41 +3271,41 @@
         <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>40600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>34300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>17600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3321,8 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3243,8 +3336,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3272,27 +3368,27 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3">
         <v>38300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>32400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>600</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,8 +3404,8 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3323,8 +3419,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3364,27 +3463,27 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>10100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,68 +3502,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E46" s="3">
         <v>323700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>353400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>186900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>216100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>189400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>245300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>326700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>410500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>464700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>434100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>427400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>389100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>382100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>172200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>216100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>265500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>105000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>129900</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,8 +3585,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3524,8 +3629,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3563,68 +3668,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>8100</v>
       </c>
       <c r="Q48" s="3">
         <v>8100</v>
       </c>
       <c r="R48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="S48" s="3">
         <v>8200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,8 +3751,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,8 +4000,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3895,7 +4015,7 @@
         <v>3500</v>
       </c>
       <c r="F52" s="3">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="G52" s="3">
         <v>1500</v>
@@ -3904,46 +4024,46 @@
         <v>1500</v>
       </c>
       <c r="I52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J52" s="3">
         <v>1900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1200</v>
       </c>
       <c r="K52" s="3">
         <v>1200</v>
       </c>
       <c r="L52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M52" s="3">
         <v>46400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11300</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1200</v>
       </c>
       <c r="Q52" s="3">
         <v>1200</v>
       </c>
       <c r="R52" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="S52" s="3">
         <v>900</v>
       </c>
       <c r="T52" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="U52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>200</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,68 +4166,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>293600</v>
+      </c>
+      <c r="E54" s="3">
         <v>332600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>362700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>194600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>219700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>193600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>250700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>332200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>417500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>517500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>466600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>453600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>408000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>391500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>181400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>225200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>274400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>105600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>130500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,8 +4313,9 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4192,59 +4323,59 @@
         <v>3500</v>
       </c>
       <c r="E57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,49 +4394,52 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2300</v>
       </c>
       <c r="L58" s="3">
         <v>2300</v>
       </c>
       <c r="M58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N58" s="3">
         <v>2200</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2100</v>
       </c>
       <c r="O58" s="3">
         <v>2100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4320,11 +4454,11 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,8 +4477,11 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4384,27 +4521,27 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>40400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>25600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,68 +4560,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E60" s="3">
         <v>22700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>70100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>91600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>82000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>64100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>51600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>46600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,50 +4643,53 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4583,8 +4726,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4624,26 +4770,26 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5800</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,68 +5058,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E66" s="3">
         <v>27400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>70900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>93000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>84000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>48200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>50800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5227,13 +5395,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>239400</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>239400</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>239400</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,68 +5504,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-792700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-751400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-718400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-684000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-642600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-606700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-569100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-496400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-423700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-304900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-309700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-330600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-352600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-354200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-311500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-257800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-203700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-155800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-127500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,68 +5836,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>273200</v>
+      </c>
+      <c r="E76" s="3">
         <v>305300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>332000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>167900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>201400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>164800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>196200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>261300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>324400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>433400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>418400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>386400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>352600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>340600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>144000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>192800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>240900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-151200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-124100</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,82 +6002,85 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5898,77 +6090,80 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-33000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-41400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-37500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-72700</v>
       </c>
       <c r="J81" s="3">
         <v>-72700</v>
       </c>
       <c r="K81" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="L81" s="3">
         <v>-118800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-53800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-54100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-47800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-28300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-59600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,8 +6173,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,8 +6206,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6023,7 +6222,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
@@ -6035,7 +6234,7 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -6044,23 +6243,23 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
+        <v>200</v>
+      </c>
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -6076,8 +6275,8 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -6088,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,77 +6702,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-36900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-25200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-59000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-41600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-66600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-49700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-43100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-46500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-40600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-28200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-46600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-13000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-12600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,17 +6818,18 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -6616,55 +6837,55 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-36200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-400</v>
       </c>
       <c r="N91" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-200</v>
       </c>
       <c r="U91" s="3">
         <v>-200</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
@@ -6678,8 +6899,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,77 +7065,80 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E94" s="3">
         <v>29500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>23000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-43700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>65000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>38800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>20900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-108100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>123200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>56000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-228200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>84000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-99300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-49200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6989,8 +7223,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,77 +7511,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>191600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>65700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>100</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>232200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>159600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>25900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,61 +7594,64 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7413,8 +7662,8 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
@@ -7428,77 +7677,80 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>166600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-95600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>34900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-112500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>133200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>40600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-43000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>60400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-26500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>63800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
